--- a/feat/migration-contenu-fhir/ig/observations-summary.xlsx
+++ b/feat/migration-contenu-fhir/ig/observations-summary.xlsx
@@ -179,7 +179,7 @@
     <t>Observation Category Codes#social-history</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-social-history-code-cisis|20260420150250 (required)</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-social-history-code-cisis|20260619134042 (required)</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
@@ -218,7 +218,7 @@
     <t>Observation Category Codes#vital-signs</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis|20260420150251 (required)</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis|20260619134043 (required)</t>
   </si>
   <si>
     <t>fr-observation-vital-signs-panel-document</t>
